--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88708</v>
+        <v>88711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88662</v>
+        <v>88665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88711</v>
+        <v>88714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88665</v>
+        <v>88668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88714</v>
+        <v>88718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88668</v>
+        <v>88672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88718</v>
+        <v>88725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88672</v>
+        <v>88679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88725</v>
+        <v>88727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88679</v>
+        <v>88681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88727</v>
+        <v>88728</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88681</v>
+        <v>88682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88728</v>
+        <v>88731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88682</v>
+        <v>88685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88731</v>
+        <v>88733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88685</v>
+        <v>88687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88733</v>
+        <v>88737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88687</v>
+        <v>88691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88737</v>
+        <v>88738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88691</v>
+        <v>88692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 48988-2025 artfynd.xlsx
+++ b/artfynd/A 48988-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129094217</v>
       </c>
       <c r="B2" t="n">
-        <v>88738</v>
+        <v>89083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>129094216</v>
       </c>
       <c r="B3" t="n">
-        <v>88692</v>
+        <v>89029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Ängsvaxing agg.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
